--- a/artfynd/A 31534-2021 artfynd.xlsx
+++ b/artfynd/A 31534-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31534-2021 artfynd.xlsx
+++ b/artfynd/A 31534-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>94745966</v>
       </c>
       <c r="B2" t="n">
-        <v>92688</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95962</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -717,10 +712,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563522.3898143703</v>
+        <v>563522</v>
       </c>
       <c r="R2" t="n">
-        <v>6711713.957275794</v>
+        <v>6711714</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,19 +745,9 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-07-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,15 +774,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>94746133</v>
+        <v>94745757</v>
       </c>
       <c r="B3" t="n">
-        <v>93868</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -823,18 +803,20 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ängelsfors, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563592.7592311621</v>
+        <v>563488</v>
       </c>
       <c r="R3" t="n">
-        <v>6711693.53816645</v>
+        <v>6711705</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,27 +846,18 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -903,15 +876,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>94751203</v>
+        <v>94745793</v>
       </c>
       <c r="B4" t="n">
-        <v>57577</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,43 +887,36 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208249</v>
+        <v>2869</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ängelsfors, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563483.452791658</v>
+        <v>563475</v>
       </c>
       <c r="R4" t="n">
-        <v>6711713.272405176</v>
+        <v>6711709</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -985,35 +946,19 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Sumpskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1030,15 +975,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>94745757</v>
+        <v>94746091</v>
       </c>
       <c r="B5" t="n">
-        <v>93868</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1064,20 +1004,18 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ängelsfors, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563487.5342299433</v>
+        <v>563557</v>
       </c>
       <c r="R5" t="n">
-        <v>6711705.468589184</v>
+        <v>6711662</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1107,28 +1045,17 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1147,15 +1074,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>94745793</v>
+        <v>94746133</v>
       </c>
       <c r="B6" t="n">
-        <v>93868</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1189,10 +1111,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563475.6533258734</v>
+        <v>563592</v>
       </c>
       <c r="R6" t="n">
-        <v>6711708.213030867</v>
+        <v>6711694</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1222,19 +1144,9 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-07-08</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,16 +1176,11 @@
         <v>94746076</v>
       </c>
       <c r="B7" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1309,10 +1216,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563532.8880657364</v>
+        <v>563533</v>
       </c>
       <c r="R7" t="n">
-        <v>6711677.717266568</v>
+        <v>6711678</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1342,19 +1249,9 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-07-08</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,15 +1278,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>94746091</v>
+        <v>94746057</v>
       </c>
       <c r="B8" t="n">
-        <v>93868</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,36 +1289,41 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2869</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ängelsfors, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563556.8234367684</v>
+        <v>563498</v>
       </c>
       <c r="R8" t="n">
-        <v>6711662.387189472</v>
+        <v>6711712</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1456,19 +1353,9 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-07-08</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1495,15 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>94746057</v>
+        <v>94745625</v>
       </c>
       <c r="B9" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1511,41 +1393,47 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>208249</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ängelsfors, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563498.2736214033</v>
+        <v>563520</v>
       </c>
       <c r="R9" t="n">
-        <v>6711711.564147122</v>
+        <v>6711568</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1575,27 +1463,18 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1611,6 +1490,118 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>94751203</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ängelsfors, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>563483</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6711714</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2021-07-08</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2021-07-08</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Sumpskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
